--- a/output/rebalance_day_2026-04-01_221613_strategy2/rebalance_day_report.xlsx
+++ b/output/rebalance_day_2026-04-01_221613_strategy2/rebalance_day_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\qqq\output\rebalance_day_2026-04-01_221613_strategy2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FAF5E2-6ABD-4DE4-8820-1A3B8ACCD417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF87FF21-A363-4679-8F9F-5D282F84E364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="6180" windowWidth="14910" windowHeight="11310" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rebalance_Config_Status" sheetId="1" r:id="rId1"/>
@@ -8241,16 +8241,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>41274</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>269874</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8277,16 +8277,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>841374</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>587374</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
